--- a/output/pdf_financials_xlsx/VLC.xlsx
+++ b/output/pdf_financials_xlsx/VLC.xlsx
@@ -5987,46 +5987,46 @@
         <v>1.119631</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.119631</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.14531</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.14531</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.14531</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.14531</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.117994</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.613959</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.703957</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.601716</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.711765</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.083722</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.505341</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.791704</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>3.071222</v>
       </c>
     </row>
     <row r="93">
@@ -7471,25 +7471,25 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.06256299999999999</v>
+        <v>-0.455263</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>1.327245</v>
+        <v>1.218411</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>1.367098</v>
+        <v>1.302507</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.0013</v>
+        <v>-0.015364</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.441596</v>
+        <v>0.433524</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.99264</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>-0.867731</v>
@@ -10172,7 +10172,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11629,7 +11633,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -12894,7 +12902,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -15829,7 +15841,11 @@
           <t>Reserves 1,117,994</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -17063,7 +17079,11 @@
           <t>Reserves (Note 5) 1,145,310</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -18497,7 +18517,11 @@
           <t>Share-based payment reserve 10</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -19705,7 +19729,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -20509,7 +20537,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -20816,7 +20848,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -21927,7 +21963,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -30091,7 +30131,11 @@
           <t>Advances – exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -30291,7 +30335,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -32864,7 +32912,11 @@
           <t>Exploration and evaluation expenditures (915,420)</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -34613,7 +34665,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VLC.xlsx
+++ b/output/pdf_financials_xlsx/VLC.xlsx
@@ -1029,16 +1029,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.08552999999999999</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.014639</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.008462000000000001</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00213</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1059,25 +1059,25 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.065604</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.04452</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.0224</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.026514</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.008413</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.029204</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.39103</v>
       </c>
     </row>
     <row r="13">
@@ -1977,16 +1977,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.797367</v>
+        <v>-0.882897</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.914717</v>
+        <v>-0.929356</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.680886</v>
+        <v>-0.689348</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.062063</v>
+        <v>-2.064193</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.817167</v>
@@ -2007,25 +2007,25 @@
         <v>-2.424091</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.608872</v>
+        <v>-2.674476</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.238467</v>
+        <v>-2.282987</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.507607</v>
+        <v>-2.530007</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.753733</v>
+        <v>-2.780247</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.849519</v>
+        <v>-1.857932</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.17625</v>
+        <v>-2.205454</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-2.283162</v>
+        <v>-2.674192</v>
       </c>
     </row>
     <row r="28">
@@ -2093,16 +2093,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.797367</v>
+        <v>-0.882897</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.914717</v>
+        <v>-0.929356</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.680886</v>
+        <v>-0.689348</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.060708</v>
+        <v>-2.062838</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.817167</v>
@@ -2123,25 +2123,25 @@
         <v>-2.424091</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.608872</v>
+        <v>-2.674476</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.238467</v>
+        <v>-2.282987</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.496363</v>
+        <v>-2.518763</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.7136</v>
+        <v>-2.740114</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.792214</v>
+        <v>-1.800627</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.160251</v>
+        <v>-2.189455</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-2.255867</v>
+        <v>-2.646897</v>
       </c>
     </row>
     <row r="30">
@@ -2400,31 +2400,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>3.525014</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.893323</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.702442</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.203625</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.078627</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.004423</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.00033</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.002405</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.833898</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.24302</v>
@@ -2516,31 +2516,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>3.525014</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.893323</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.024</v>
+        <v>0.726442</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.01</v>
+        <v>0.213625</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.006</v>
+        <v>0.08462699999999999</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.0015</v>
+        <v>0.005923</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.002</v>
+        <v>0.00233</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.002405</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.833898</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.24302</v>
@@ -3212,31 +3212,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.547184</v>
+        <v>0.02217</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.895806</v>
+        <v>0.002483</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.711385</v>
+        <v>0.008943</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.206108</v>
+        <v>0.002483</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.078627</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.004423</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.00033</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.002405</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.9714</v>
+        <v>0.137502</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.330725</v>
@@ -7843,25 +7843,25 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.032474</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.049369</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0563</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.09002</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.131883</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.114646</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.069101</v>
       </c>
     </row>
     <row r="125">
@@ -7901,25 +7901,25 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.032474</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.049369</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0563</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.09002</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.131883</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.114646</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.069101</v>
       </c>
     </row>
     <row r="126">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -18927,7 +18927,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
@@ -24976,7 +24976,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -40104,7 +40108,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -40207,7 +40211,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -42163,7 +42167,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -42260,7 +42264,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -44141,7 +44145,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -45145,7 +45149,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -50052,7 +50056,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -50155,7 +50159,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -60946,7 +60950,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -62354,7 +62358,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E539" s="5" t="n">
